--- a/backend/templates/order-template.xlsx
+++ b/backend/templates/order-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aladd\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aladd\Desktop\Шаблоны для Сайта\Шаблон счета клиента при выгрузке (Доработать, поместить в проект)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E55C953-5C71-4BF9-9AD4-6FA731EEA424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1F6D10-3CB8-473F-8B59-579DC7173B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="156" yWindow="1116" windowWidth="16116" windowHeight="10224" tabRatio="400" xr2:uid="{C37FB294-685A-4C93-9FF2-884E3118AF7C}"/>
+    <workbookView xWindow="3720" yWindow="816" windowWidth="16416" windowHeight="11052" tabRatio="400" xr2:uid="{3A2A7C3D-03FB-4545-956A-6D915ADA5844}"/>
   </bookViews>
   <sheets>
     <sheet name="Страница 0" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t xml:space="preserve">Продавец: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.06.2026 Товарный чек № 5099 </t>
   </si>
   <si>
     <t>Заказчик:</t>
@@ -53,18 +50,9 @@
     <t>Сумма</t>
   </si>
   <si>
-    <t>Грунт по металлу серый 1 л</t>
-  </si>
-  <si>
     <t>шт</t>
   </si>
   <si>
-    <t>Краска Slaven по металлу Без запаха, зеленый 3,2 л</t>
-  </si>
-  <si>
-    <t>Уайт - спирит 1 л</t>
-  </si>
-  <si>
     <t>Доставка</t>
   </si>
   <si>
@@ -80,13 +68,16 @@
     <t>ВАЖНО: Товар принимается сразу при выгрузке из машины.</t>
   </si>
   <si>
-    <t>Адрес доставки: улица Панфилова</t>
-  </si>
-  <si>
     <t>Сумма прописью:  рублей 00 копеек. Без НДС.</t>
   </si>
   <si>
     <t>Разгрузка</t>
+  </si>
+  <si>
+    <t>Адрес доставки:</t>
+  </si>
+  <si>
+    <t>05.07.2026 Товарный чек № 0000</t>
   </si>
 </sst>
 </file>
@@ -155,7 +146,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="8"/>
       </bottom>
       <diagonal/>
@@ -164,7 +155,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="8"/>
       </bottom>
       <diagonal/>
@@ -197,31 +188,31 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -540,8 +531,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAEABB91-BD1E-4F35-918B-E7E279675ABA}">
-  <dimension ref="A1:I19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2484FBB6-2134-4CED-A57B-B30E810CF2B3}">
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.26953125" customWidth="1"/>
@@ -570,7 +561,7 @@
     </row>
     <row r="2" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -580,259 +571,207 @@
     </row>
     <row r="3" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
+      <c r="A4" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
     </row>
     <row r="5" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
+      <c r="A6" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
     </row>
     <row r="7" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>3</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>4</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="16" t="s">
         <v>6</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>7</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>1</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="9"/>
+      <c r="B8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="7"/>
       <c r="D8" s="2">
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="10">
-        <v>1</v>
-      </c>
-      <c r="G8" s="10"/>
+        <v>9</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8"/>
       <c r="H8" s="5">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="I8" s="5">
         <f>H8*D8</f>
-        <v>700</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>2</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="9"/>
+      <c r="B9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="7"/>
       <c r="D9" s="2">
         <v>1</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="10">
-        <v>3.2</v>
-      </c>
-      <c r="G9" s="10"/>
+        <v>9</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8"/>
       <c r="H9" s="5">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5">
-        <f>H9*D9</f>
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="I9:I10" si="0">H9*D9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>3</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="9"/>
+      <c r="B10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="7"/>
       <c r="D10" s="2">
         <v>1</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0</v>
+      </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="5">
-        <v>150</v>
-      </c>
-      <c r="I10" s="5">
-        <f>H10*D10</f>
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>4</v>
-      </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="6">
+        <f>SUM(I8:I10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="12">
+        <f>SUM(F8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="2">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="10">
-        <v>0</v>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="5">
-        <v>2700</v>
-      </c>
-      <c r="I11" s="5">
-        <f>H11*D11</f>
-        <v>2700</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>5</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="10">
-        <v>0</v>
-      </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="5">
-        <v>2700</v>
-      </c>
-      <c r="I12" s="5">
-        <f>H12*D12</f>
-        <v>2700</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="6">
-        <f>SUM(I8:I12)</f>
-        <v>8450</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="13">
-        <f>SUM(F8:G10)</f>
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-    </row>
-    <row r="18" spans="1:9" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="18">
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="A1:I1"/>
@@ -841,20 +780,16 @@
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="F7:G7"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="A13:H14"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A11:H12"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D13:H13"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="F9:G9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="F11:G11"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" errors="blank" horizontalDpi="300" verticalDpi="300"/>
